--- a/src/templates/Form_Absen.xlsx
+++ b/src/templates/Form_Absen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomat/Documents/Projek Mobile App/apiAbsen/src/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62041F93-1B7C-E04B-ACD0-8770D449692B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8147233B-4877-474B-8746-7DD2CC128000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'TEMPLATE 1'!$A$1:$J$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'TEMPLATE 1'!$11:$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
